--- a/attachments/DSJ_AE_Sourcing_Procurement_Purchasing_and_Logistics.xlsx
+++ b/attachments/DSJ_AE_Sourcing_Procurement_Purchasing_and_Logistics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liangfeiqiu\Dropbox\UF\Review\DSJ EIC\DSJ EIC\DSJ board\Finalized\DSJ AEs and ERBs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liangfeiqiu\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1488C4-833C-4752-99CB-6D4019614042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23CFD29-6F04-4E5F-A6D8-9FA865E35594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_E30BD9D3_88B7_4E4F_8462_579F359F9924_.wvu.FilterData" localSheetId="0" hidden="1">'Form Responses 1'!$A$1:$L$54</definedName>
+    <definedName name="Z_E30BD9D3_88B7_4E4F_8462_579F359F9924_.wvu.FilterData" localSheetId="0" hidden="1">'Form Responses 1'!$A$1:$L$55</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <customWorkbookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="252">
   <si>
     <t>First Name</t>
   </si>
@@ -806,6 +806,18 @@
   </si>
   <si>
     <t>Stochastic Dynamic Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harish </t>
+  </si>
+  <si>
+    <t>Guda</t>
+  </si>
+  <si>
+    <t>hguda@asu.edu</t>
+  </si>
+  <si>
+    <t>Arizona State University</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1167,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z1006"/>
+  <dimension ref="A1:Z1007"/>
   <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.88671875" style="2" customWidth="1"/>
@@ -1788,430 +1800,430 @@
       <c r="Y17" s="13"/>
       <c r="Z17" s="13"/>
     </row>
-    <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="8" t="s">
+    <row r="18" spans="1:26" s="9" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="13"/>
+    </row>
+    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-    </row>
-    <row r="19" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="P19" s="3"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
     </row>
     <row r="20" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="I20" s="3" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="P20" s="3"/>
     </row>
     <row r="21" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="I21" s="3" t="s">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="P21" s="3"/>
     </row>
     <row r="22" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>115</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
       <c r="P22" s="3"/>
     </row>
     <row r="23" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>121</v>
+        <v>18</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+        <v>113</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="P23" s="3"/>
     </row>
     <row r="24" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="P24" s="3"/>
     </row>
     <row r="25" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>136</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="L25" s="3"/>
       <c r="P25" s="3"/>
     </row>
     <row r="26" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>121</v>
+        <v>18</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>142</v>
+        <v>20</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="L26" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="P26" s="3"/>
     </row>
     <row r="27" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>153</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="L27" s="3"/>
     </row>
     <row r="28" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>28</v>
+        <v>149</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>50</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3" t="s">
-        <v>34</v>
+        <v>154</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>160</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>42</v>
+        <v>159</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>50</v>
@@ -2219,55 +2231,57 @@
     </row>
     <row r="30" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3" t="s">
-        <v>163</v>
+        <v>34</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>164</v>
+        <v>35</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>165</v>
+        <v>36</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>167</v>
+        <v>38</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="I30" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="L30" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="31" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>166</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>17</v>
@@ -2276,58 +2290,70 @@
         <v>18</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I32" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="L31" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
     </row>
     <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>17</v>
@@ -2341,17 +2367,17 @@
     </row>
     <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>17</v>
@@ -2365,17 +2391,17 @@
     </row>
     <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>17</v>
@@ -2389,17 +2415,17 @@
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>17</v>
@@ -2413,17 +2439,17 @@
     </row>
     <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>17</v>
@@ -2437,17 +2463,17 @@
     </row>
     <row r="38" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>17</v>
@@ -2461,17 +2487,17 @@
     </row>
     <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>17</v>
@@ -2485,17 +2511,17 @@
     </row>
     <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>17</v>
@@ -2503,23 +2529,23 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
     </row>
     <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>225</v>
+        <v>85</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>17</v>
@@ -2527,23 +2553,23 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>17</v>
@@ -2555,13 +2581,36 @@
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
     </row>
-    <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="J44" s="14"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-    </row>
-    <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="J45" s="14"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+    </row>
     <row r="46" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="48" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -2570,21 +2619,21 @@
     <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="52" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="53" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="54" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="15"/>
-    </row>
-    <row r="55" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="54" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="55" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="15"/>
+    </row>
     <row r="56" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="57" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="58" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3536,11 +3585,12 @@
     <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{E30BD9D3-88B7-4E4F-8462-579F359F9924}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:L48" xr:uid="{F037FFFD-AC1D-498A-A52A-2A802ED3E595}"/>
+      <autoFilter ref="A1:L48" xr:uid="{BCB501CF-40D5-496A-AA86-BE25157447FE}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="1905533167"/>
@@ -3549,9 +3599,9 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="3">
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="J41:L41"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
